--- a/scanlag_data/CASP+SHX/scanlag_summary.xlsx
+++ b/scanlag_data/CASP+SHX/scanlag_summary.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/along/Documents/Projects/manuscript_reviews/scanlag_data/CASP+SHX/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Projects\manuscript_reviews\scanlag_data\CASP+SHX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EE94E6-C6A5-E24B-84C1-F5D5AA042C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBEAD0C-2DC4-4FE0-8128-2E8CEF3EA3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19580" xr2:uid="{9DEF8DDA-6DDB-4E4E-9FF3-E592AEBCB150}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DEF8DDA-6DDB-4E4E-9FF3-E592AEBCB150}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
   <si>
     <t>Study</t>
   </si>
@@ -68,9 +68,6 @@
     <t>KLYR</t>
   </si>
   <si>
-    <t>nutrient depletion</t>
-  </si>
-  <si>
     <t>SHX</t>
   </si>
   <si>
@@ -86,16 +83,16 @@
     <t>Kaplan et. al</t>
   </si>
   <si>
-    <t>Sodium azide</t>
-  </si>
-  <si>
-    <t>CAM</t>
-  </si>
-  <si>
-    <t>KLY</t>
-  </si>
-  <si>
-    <t>LB starvation</t>
+    <t>Reg-Arrest</t>
+  </si>
+  <si>
+    <t>Reg-Arrest+SHX</t>
+  </si>
+  <si>
+    <t>Reg-Arrest+aTc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -467,18 +464,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E457E291-D01C-B541-803B-36EDD8A0F93E}">
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="16" max="16" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,19 +508,16 @@
         <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -545,72 +540,66 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K2" t="s">
         <v>8</v>
       </c>
       <c r="L2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
       <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
         <v>9</v>
       </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
       <c r="L3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -633,7 +622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -668,16 +657,13 @@
         <v>-91</v>
       </c>
       <c r="L5">
-        <v>-91</v>
+        <v>-48</v>
       </c>
       <c r="M5">
-        <v>-106</v>
-      </c>
-      <c r="N5">
-        <v>-75</v>
+        <v>-62</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -712,16 +698,13 @@
         <v>203.41916747337851</v>
       </c>
       <c r="L6">
-        <v>104.1258064516129</v>
+        <v>105.92408376963351</v>
       </c>
       <c r="M6">
-        <v>223.13593380614657</v>
-      </c>
-      <c r="N6">
-        <v>125.00400801603206</v>
+        <v>93.207900207900209</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -756,13 +739,15 @@
         <v>298.75333591028448</v>
       </c>
       <c r="L7">
-        <v>110.78073780806896</v>
+        <v>46.585697601508137</v>
       </c>
       <c r="M7">
-        <v>137.10823853473354</v>
-      </c>
-      <c r="N7">
-        <v>134.72028132679586</v>
+        <v>49.263920961294644</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M12" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/scanlag_data/CASP+SHX/scanlag_summary.xlsx
+++ b/scanlag_data/CASP+SHX/scanlag_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Projects\manuscript_reviews\scanlag_data\CASP+SHX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBEAD0C-2DC4-4FE0-8128-2E8CEF3EA3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81C0148-5720-49E1-A270-30C3D6EFBD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9DEF8DDA-6DDB-4E4E-9FF3-E592AEBCB150}"/>
   </bookViews>
@@ -627,40 +627,40 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="C5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="D5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="E5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="F5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="G5">
-        <v>1011</v>
+        <v>1146</v>
       </c>
       <c r="H5">
-        <v>-59</v>
+        <v>16</v>
       </c>
       <c r="I5">
-        <v>-59</v>
+        <v>16</v>
       </c>
       <c r="J5">
-        <v>-59</v>
+        <v>16</v>
       </c>
       <c r="K5">
-        <v>-91</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>-48</v>
+        <v>72</v>
       </c>
       <c r="M5">
-        <v>-62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
